--- a/resources/ctq_sheet_oos_decoration.xlsx
+++ b/resources/ctq_sheet_oos_decoration.xlsx
@@ -20,9 +20,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -53,9 +52,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -813,59 +813,6 @@
         <is>
           <t>flag</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ARRAY</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Z571</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1B990</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>RC_3</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>L3Z76700630</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>46223.489375</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.278268</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.087841</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.1111628166666667</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>USL</t>
-        </is>
-      </c>
-      <c r="M2" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/resources/ctq_sheet_oos_decoration.xlsx
+++ b/resources/ctq_sheet_oos_decoration.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="M626" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="M673" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="M678" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Z517" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Z571" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="M673" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="M678" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Z517" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Z571" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="M626" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/resources/ctq_sheet_oos_decoration.xlsx
+++ b/resources/ctq_sheet_oos_decoration.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="M673" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="M678" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Z517" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Z571" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="M626" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M673" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M678" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z517" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z571" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M626" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/resources/ctq_sheet_oos_decoration.xlsx
+++ b/resources/ctq_sheet_oos_decoration.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M673" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M678" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z517" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z571" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M626" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="M673" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="M678" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Z517" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Z571" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="M626" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/resources/ctq_sheet_oos_decoration.xlsx
+++ b/resources/ctq_sheet_oos_decoration.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="M673" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="M678" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Z517" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Z571" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="M626" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="M626" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="M673" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="M678" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Z517" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Z571" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,8 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -52,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -583,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -651,6 +653,59 @@
         <is>
           <t>flag</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ARRAY</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>M678</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1A240</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SE_L1T</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>L3MR6701808</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>46249.75216435185</v>
+      </c>
+      <c r="G2" t="n">
+        <v>79.559</v>
+      </c>
+      <c r="H2" t="n">
+        <v>61.893</v>
+      </c>
+      <c r="I2" t="n">
+        <v>73.31207142857143</v>
+      </c>
+      <c r="J2" t="n">
+        <v>87.75</v>
+      </c>
+      <c r="K2" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>LSL</t>
+        </is>
+      </c>
+      <c r="M2" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
